--- a/erp-server/erp-server-file/src/main/resources/excel/plm/productNoSpecDetailExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/plm/productNoSpecDetailExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="23130" windowHeight="11850"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
   <si>
     <t>spu</t>
   </si>
@@ -1002,6 +1002,12 @@
     <t>单箱数量</t>
   </si>
   <si>
+    <t>推荐仓位(小货区)</t>
+  </si>
+  <si>
+    <t>推荐仓位(大货区)</t>
+  </si>
+  <si>
     <t>{.spuNo}</t>
   </si>
   <si>
@@ -1206,22 +1212,22 @@
     <t>{.englishUsage}</t>
   </si>
   <si>
-    <t>{.productSizeLength}</t>
-  </si>
-  <si>
-    <t>{.productSizeWide}</t>
-  </si>
-  <si>
-    <t>{.productSizeHigh}</t>
-  </si>
-  <si>
-    <t>{.boxSizeLength}</t>
-  </si>
-  <si>
-    <t>{.boxSizeWide}</t>
-  </si>
-  <si>
-    <t>{.boxSizeHigh}</t>
+    <t>{.productLength}</t>
+  </si>
+  <si>
+    <t>{.productWidth}</t>
+  </si>
+  <si>
+    <t>{.productHeight}</t>
+  </si>
+  <si>
+    <t>{.boxLength}</t>
+  </si>
+  <si>
+    <t>{.boxWidth}</t>
+  </si>
+  <si>
+    <t>{.boxHeight}</t>
   </si>
   <si>
     <t>{.grossWeight}</t>
@@ -1234,6 +1240,12 @@
   </si>
   <si>
     <t>{.boxQty}</t>
+  </si>
+  <si>
+    <t>{.warehouseLocation}</t>
+  </si>
+  <si>
+    <t>{.warehouseLocationLarge}</t>
   </si>
 </sst>
 </file>
@@ -1918,8 +1930,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1956,6 +1971,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2277,7 +2295,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BZ3"/>
+  <dimension ref="A1:CB3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
     <col min="2" max="2" width="12.875" customWidth="1"/>
@@ -2339,484 +2357,498 @@
     <col min="64" max="64" width="10.75" customWidth="1"/>
     <col min="65" max="65" width="10.625" customWidth="1"/>
     <col min="66" max="68" width="11.125" customWidth="1"/>
-    <col min="69" max="70" width="11" customWidth="1"/>
+    <col min="69" max="69" width="18.75" customWidth="1"/>
+    <col min="70" max="70" width="11" customWidth="1"/>
     <col min="71" max="71" width="10.375" customWidth="1"/>
+    <col min="79" max="80" width="11.125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:78">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:80">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="U1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="Y1" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="Z1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AA1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="4" t="s">
+      <c r="AB1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="4" t="s">
+      <c r="AC1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="4" t="s">
+      <c r="AD1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="4" t="s">
+      <c r="AE1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="7" t="s">
+      <c r="AG1" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="7" t="s">
+      <c r="AH1" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="7" t="s">
+      <c r="AI1" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="7" t="s">
+      <c r="AJ1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="8" t="s">
+      <c r="AK1" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="5" t="s">
+      <c r="AL1" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="5" t="s">
+      <c r="AM1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="5" t="s">
+      <c r="AN1" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="7" t="s">
+      <c r="AO1" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AP1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AR1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AS1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="9" t="s">
+      <c r="AT1" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="4" t="s">
+      <c r="AU1" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="9" t="s">
+      <c r="AV1" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="4" t="s">
+      <c r="AW1" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="9" t="s">
+      <c r="AX1" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="2" t="s">
+      <c r="AY1" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="AZ1" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="BA1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="5" t="s">
+      <c r="BB1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="2" t="s">
+      <c r="BC1" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BD1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="2" t="s">
+      <c r="BE1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="2" t="s">
+      <c r="BF1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BG1" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" s="11" t="s">
+      <c r="BH1" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BI1" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BJ1" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BK1" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BL1" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BM1" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BN1" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BO1" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BP1" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="BQ1" s="12" t="s">
+      <c r="BQ1" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="BR1" s="12" t="s">
+      <c r="BR1" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="BS1" s="12" t="s">
+      <c r="BS1" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="BT1" s="12" t="s">
+      <c r="BT1" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="BU1" s="12" t="s">
+      <c r="BU1" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="BV1" s="12" t="s">
+      <c r="BV1" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="BW1" s="12" t="s">
+      <c r="BW1" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="BX1" s="12" t="s">
+      <c r="BX1" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="BY1" s="12" t="s">
+      <c r="BY1" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="BZ1" s="7" t="s">
+      <c r="BZ1" s="8" t="s">
         <v>77</v>
       </c>
+      <c r="CA1" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="CB1" s="14" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="2" spans="1:78">
-      <c r="A2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2" s="1" t="s">
+    <row r="2" spans="1:80">
+      <c r="A2" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="L2" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="M2" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="N2" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="O2" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="P2" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="Q2" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="R2" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="S2" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="T2" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="U2" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="V2" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="W2" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="X2" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="Y2" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="Z2" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AA2" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="AD2" s="1" t="s">
+      <c r="AB2" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="AE2" s="1" t="s">
+      <c r="AC2" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="AF2" s="1" t="s">
+      <c r="AD2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="AG2" s="1" t="s">
+      <c r="AE2" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="AH2" s="1" t="s">
+      <c r="AF2" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="AI2" s="1" t="s">
+      <c r="AG2" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="AJ2" s="1" t="s">
+      <c r="AH2" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="AK2" s="1" t="s">
+      <c r="AI2" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="AL2" s="1" t="s">
+      <c r="AJ2" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="AM2" s="1" t="s">
+      <c r="AK2" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="AN2" s="1" t="s">
+      <c r="AL2" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="AO2" s="1" t="s">
+      <c r="AM2" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="AP2" s="1" t="s">
+      <c r="AN2" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="AQ2" s="1" t="s">
+      <c r="AO2" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="AR2" s="1" t="s">
+      <c r="AP2" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="AS2" s="1" t="s">
+      <c r="AQ2" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="AT2" s="1" t="s">
+      <c r="AR2" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="AU2" s="1" t="s">
+      <c r="AS2" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="AV2" s="1" t="s">
+      <c r="AT2" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="AW2" s="1" t="s">
+      <c r="AU2" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="AX2" s="1" t="s">
+      <c r="AV2" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="AY2" s="1" t="s">
+      <c r="AW2" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="AZ2" s="1" t="s">
+      <c r="AX2" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="BA2" s="1" t="s">
+      <c r="AY2" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="BB2" s="1" t="s">
+      <c r="AZ2" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="BC2" s="1" t="s">
+      <c r="BA2" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="BD2" s="1" t="s">
+      <c r="BB2" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="BE2" s="1" t="s">
+      <c r="BC2" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="BF2" s="1" t="s">
+      <c r="BD2" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="BG2" s="1" t="s">
+      <c r="BE2" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="BH2" s="1" t="s">
+      <c r="BF2" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="BI2" s="1" t="s">
+      <c r="BG2" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="BJ2" s="1" t="s">
+      <c r="BH2" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="BK2" s="1" t="s">
+      <c r="BI2" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="BL2" s="1" t="s">
+      <c r="BJ2" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="BM2" s="1" t="s">
+      <c r="BK2" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="BN2" s="1" t="s">
+      <c r="BL2" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="BO2" s="1" t="s">
+      <c r="BM2" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="BP2" s="1" t="s">
+      <c r="BN2" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="BQ2" s="1" t="s">
+      <c r="BO2" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="BR2" s="1" t="s">
+      <c r="BP2" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="BS2" s="1" t="s">
+      <c r="BQ2" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="BT2" s="1" t="s">
+      <c r="BR2" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="BU2" s="1" t="s">
+      <c r="BS2" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="BV2" s="1" t="s">
+      <c r="BT2" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="BW2" s="1" t="s">
+      <c r="BU2" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="BX2" s="1" t="s">
+      <c r="BV2" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="BY2" s="1" t="s">
+      <c r="BW2" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="BZ2" s="1" t="s">
+      <c r="BX2" s="2" t="s">
         <v>155</v>
+      </c>
+      <c r="BY2" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="BZ2" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="CA2" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="CB2" s="14" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="54:54">
-      <c r="BB3" s="10"/>
+      <c r="BB3" s="11"/>
     </row>
   </sheetData>
   <dataValidations count="9">
